--- a/src/node/uploads/yellow.xlsx
+++ b/src/node/uploads/yellow.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="15945" windowHeight="7095"/>
   </bookViews>
   <sheets>
     <sheet name="yellow" sheetId="1" r:id="rId1"/>
@@ -27,39 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1356" uniqueCount="1356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1347" uniqueCount="1347">
   <si>
     <t>timestamp</t>
   </si>
   <si>
     <t>displ</t>
-  </si>
-  <si>
-    <t>2022-01-01 14:00:00 UTC</t>
-  </si>
-  <si>
-    <t>2022-01-01 15:00:00 UTC</t>
-  </si>
-  <si>
-    <t>2022-01-01 16:00:00 UTC</t>
-  </si>
-  <si>
-    <t>2022-01-01 17:00:00 UTC</t>
-  </si>
-  <si>
-    <t>2022-01-01 18:00:00 UTC</t>
-  </si>
-  <si>
-    <t>2022-01-01 19:00:00 UTC</t>
-  </si>
-  <si>
-    <t>2022-01-01 20:00:00 UTC</t>
-  </si>
-  <si>
-    <t>2022-01-01 21:00:00 UTC</t>
-  </si>
-  <si>
-    <t>2022-01-01 22:00:00 UTC</t>
   </si>
   <si>
     <t>2022-01-01 23:00:00 UTC</t>
@@ -5249,6 +5222,10 @@
   <sheetPr/>
   <dimension ref="A1:B1355"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="29.125" customWidth="1"/>
+    <col min="2" max="2" width="13.75"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -16018,74 +15995,47 @@
         <v>75.64836342</v>
       </c>
     </row>
-    <row r="1347" spans="1:2">
-      <c r="A1347" t="s">
-        <v>1347</v>
-      </c>
+    <row r="1347" spans="2:2">
       <c r="B1347">
         <v>76.19359282</v>
       </c>
     </row>
-    <row r="1348" spans="1:2">
-      <c r="A1348" t="s">
-        <v>1348</v>
-      </c>
+    <row r="1348" spans="2:2">
       <c r="B1348">
         <v>77.66910049</v>
       </c>
     </row>
-    <row r="1349" spans="1:2">
-      <c r="A1349" t="s">
-        <v>1349</v>
-      </c>
+    <row r="1349" spans="2:2">
       <c r="B1349">
         <v>77.90468859</v>
       </c>
     </row>
-    <row r="1350" spans="1:2">
-      <c r="A1350" t="s">
-        <v>1350</v>
-      </c>
+    <row r="1350" spans="2:2">
       <c r="B1350">
         <v>78.82976469</v>
       </c>
     </row>
-    <row r="1351" spans="1:2">
-      <c r="A1351" t="s">
-        <v>1351</v>
-      </c>
+    <row r="1351" spans="2:2">
       <c r="B1351">
         <v>80.26120644</v>
       </c>
     </row>
-    <row r="1352" spans="1:2">
-      <c r="A1352" t="s">
-        <v>1352</v>
-      </c>
+    <row r="1352" spans="2:2">
       <c r="B1352">
         <v>81.35469055</v>
       </c>
     </row>
-    <row r="1353" spans="1:2">
-      <c r="A1353" t="s">
-        <v>1353</v>
-      </c>
+    <row r="1353" spans="2:2">
       <c r="B1353">
         <v>82.34425908</v>
       </c>
     </row>
-    <row r="1354" spans="1:2">
-      <c r="A1354" t="s">
-        <v>1354</v>
-      </c>
+    <row r="1354" spans="2:2">
       <c r="B1354">
         <v>83.08406504</v>
       </c>
     </row>
-    <row r="1355" spans="1:2">
-      <c r="A1355" t="s">
-        <v>1355</v>
-      </c>
+    <row r="1355" spans="2:2">
       <c r="B1355">
         <v>83.2779215</v>
       </c>

--- a/src/node/uploads/yellow.xlsx
+++ b/src/node/uploads/yellow.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="15945" windowHeight="7095"/>
+    <workbookView windowWidth="27950" windowHeight="12280"/>
   </bookViews>
   <sheets>
     <sheet name="yellow" sheetId="1" r:id="rId1"/>
@@ -5220,11 +5220,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B1355"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <dimension ref="A1:B1346"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="29.125" customWidth="1"/>
-    <col min="2" max="2" width="13.75"/>
+    <col min="1" max="1" width="29.1272727272727" customWidth="1"/>
+    <col min="2" max="2" width="13.7545454545455"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -15995,51 +15995,6 @@
         <v>75.64836342</v>
       </c>
     </row>
-    <row r="1347" spans="2:2">
-      <c r="B1347">
-        <v>76.19359282</v>
-      </c>
-    </row>
-    <row r="1348" spans="2:2">
-      <c r="B1348">
-        <v>77.66910049</v>
-      </c>
-    </row>
-    <row r="1349" spans="2:2">
-      <c r="B1349">
-        <v>77.90468859</v>
-      </c>
-    </row>
-    <row r="1350" spans="2:2">
-      <c r="B1350">
-        <v>78.82976469</v>
-      </c>
-    </row>
-    <row r="1351" spans="2:2">
-      <c r="B1351">
-        <v>80.26120644</v>
-      </c>
-    </row>
-    <row r="1352" spans="2:2">
-      <c r="B1352">
-        <v>81.35469055</v>
-      </c>
-    </row>
-    <row r="1353" spans="2:2">
-      <c r="B1353">
-        <v>82.34425908</v>
-      </c>
-    </row>
-    <row r="1354" spans="2:2">
-      <c r="B1354">
-        <v>83.08406504</v>
-      </c>
-    </row>
-    <row r="1355" spans="2:2">
-      <c r="B1355">
-        <v>83.2779215</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/src/node/uploads/yellow.xlsx
+++ b/src/node/uploads/yellow.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27950" windowHeight="12280"/>
+    <workbookView windowWidth="15945" windowHeight="7095"/>
   </bookViews>
   <sheets>
     <sheet name="yellow" sheetId="1" r:id="rId1"/>
@@ -5220,11 +5220,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B1346"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
+  <dimension ref="A1:B1355"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="29.1272727272727" customWidth="1"/>
-    <col min="2" max="2" width="13.7545454545455"/>
+    <col min="1" max="1" width="29.125" customWidth="1"/>
+    <col min="2" max="2" width="13.75"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -15995,6 +15995,51 @@
         <v>75.64836342</v>
       </c>
     </row>
+    <row r="1347" spans="2:2">
+      <c r="B1347">
+        <v>76.19359282</v>
+      </c>
+    </row>
+    <row r="1348" spans="2:2">
+      <c r="B1348">
+        <v>77.66910049</v>
+      </c>
+    </row>
+    <row r="1349" spans="2:2">
+      <c r="B1349">
+        <v>77.90468859</v>
+      </c>
+    </row>
+    <row r="1350" spans="2:2">
+      <c r="B1350">
+        <v>78.82976469</v>
+      </c>
+    </row>
+    <row r="1351" spans="2:2">
+      <c r="B1351">
+        <v>80.26120644</v>
+      </c>
+    </row>
+    <row r="1352" spans="2:2">
+      <c r="B1352">
+        <v>81.35469055</v>
+      </c>
+    </row>
+    <row r="1353" spans="2:2">
+      <c r="B1353">
+        <v>82.34425908</v>
+      </c>
+    </row>
+    <row r="1354" spans="2:2">
+      <c r="B1354">
+        <v>83.08406504</v>
+      </c>
+    </row>
+    <row r="1355" spans="2:2">
+      <c r="B1355">
+        <v>83.2779215</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
